--- a/StructureDefinition-ct-anterior-surface.xlsx
+++ b/StructureDefinition-ct-anterior-surface.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T00:41:24+00:00</t>
+    <t>2026-08-25T02:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ct-anterior-surface.xlsx
+++ b/StructureDefinition-ct-anterior-surface.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T02:25:39+00:00</t>
+    <t>2026-08-25T18:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ct-anterior-surface.xlsx
+++ b/StructureDefinition-ct-anterior-surface.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T18:52:20+00:00</t>
+    <t>2026-09-01T17:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -762,7 +762,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ophthalmic-encounter)
 </t>
   </si>
   <si>
@@ -3092,7 +3092,7 @@
     <t>Observation.component:vertexLoc.code</t>
   </si>
   <si>
-    <t>DICOM (0046,0202)</t>
+    <t>Corneal vertex location - corneal vertex position coordinates. DICOM (0046,0202)</t>
   </si>
   <si>
     <t>Observation.component:vertexLoc.value[x]</t>
@@ -3125,7 +3125,7 @@
     <t>Observation.component:pupilCentroidX.code</t>
   </si>
   <si>
-    <t>DICOM (0046,0203)</t>
+    <t>Pupil centroid X - X-coordinate of pupil center. DICOM (0046,0203)</t>
   </si>
   <si>
     <t>Observation.component:pupilCentroidX.value[x]</t>
@@ -3158,7 +3158,7 @@
     <t>Observation.component:pupilCentroidY.code</t>
   </si>
   <si>
-    <t>DICOM (0046,0204)</t>
+    <t>Pupil centroid Y - Y-coordinate of pupil center. DICOM (0046,0204)</t>
   </si>
   <si>
     <t>Observation.component:pupilCentroidY.value[x]</t>
@@ -3191,7 +3191,7 @@
     <t>Observation.component:pupilRadius.code</t>
   </si>
   <si>
-    <t>DICOM (0046,0205)</t>
+    <t>Equivalent pupil radius - radius of equivalent circular pupil. DICOM (0046,0205)</t>
   </si>
   <si>
     <t>Observation.component:pupilRadius.value[x]</t>
@@ -3224,7 +3224,7 @@
     <t>Observation.component:mapType.code</t>
   </si>
   <si>
-    <t>DICOM (0046,0207)</t>
+    <t>Map type - type of topographic map encoded (axial, tangential, elevation, refractive, pachymetry). DICOM (0046,0207)</t>
   </si>
   <si>
     <t>Observation.component:mapType.value[x]</t>
@@ -3257,7 +3257,7 @@
     <t>Observation.component:analyzedArea.code</t>
   </si>
   <si>
-    <t>DICOM (0046,0227)</t>
+    <t>Analyzed area - total area of cornea analyzed. DICOM (0046,0227)</t>
   </si>
   <si>
     <t>Observation.component:analyzedArea.value[x]</t>
@@ -3290,7 +3290,7 @@
     <t>Observation.component:eccentricity.code</t>
   </si>
   <si>
-    <t>DICOM (0046,0234)</t>
+    <t>Corneal eccentricity index - corneal eccentricity (shape factor). DICOM (0046,0234)</t>
   </si>
   <si>
     <t>Observation.component:eccentricity.value[x]</t>
@@ -3323,7 +3323,7 @@
     <t>Observation.component:kpi.code</t>
   </si>
   <si>
-    <t>DICOM (0046,0236)</t>
+    <t>Keratoconus prediction index (KPI) - corneal KC prediction index, different from KISA%. DICOM (0046,0236)</t>
   </si>
   <si>
     <t>Observation.component:kpi.value[x]</t>
@@ -3356,7 +3356,7 @@
     <t>Observation.component:potentialVA.code</t>
   </si>
   <si>
-    <t>DICOM (0046,0238)</t>
+    <t>Decimal potential visual acuity - estimated potential VA from corneal surface. DICOM (0046,0238)</t>
   </si>
   <si>
     <t>Observation.component:potentialVA.value[x]</t>
@@ -5915,7 +5915,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>233</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>83</v>
@@ -6037,7 +6037,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>244</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>83</v>
